--- a/all_sim/det_gemini_pet.xlsx
+++ b/all_sim/det_gemini_pet.xlsx
@@ -332,15 +332,15 @@
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.4294532627865962</v>
+        <v>0.6678516313932981</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.638888888888889</v>
+        <v>0.8042929292929293</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.38333333333333336</v>
+        <v>0.6769607843137255</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.6785714285714285</v>
+        <v>0.8231566820276497</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -464,31 +464,31 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.7738095238095237</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.7738095238095237</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.7738095238095237</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.7738095238095237</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.7238095238095238</v>
+        <v>0.861904761904762</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.6904761904761904</v>
+        <v>0.8452380952380951</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.6904761904761904</v>
+        <v>0.8452380952380951</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.6904761904761904</v>
+        <v>0.8452380952380951</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.6904761904761904</v>
+        <v>0.8452380952380951</v>
       </c>
     </row>
     <row r="5">
@@ -510,22 +510,22 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -544,25 +544,25 @@
         <v>1.0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9690970545630131</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.7650462962962963</v>
+        <v>0.8779359921848454</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.5274656150301249</v>
+        <v>0.7589709027531577</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.5271370815969719</v>
+        <v>0.7588066360365813</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.534278120188945</v>
+        <v>0.7623313677867802</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.5228451736623996</v>
+        <v>0.7566148945235075</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.5228451736623996</v>
+        <v>0.7566148945235075</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.5228451736623996</v>
+        <v>0.7566148945235075</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.5228451736623996</v>
+        <v>0.7566148945235075</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.5228451736623996</v>
+        <v>0.7566148945235075</v>
       </c>
     </row>
     <row r="8">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9744296285490506</v>
+        <v>0.9872148142745253</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.9744296285490506</v>
+        <v>0.9872148142745253</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>1.0</v>
@@ -624,19 +624,19 @@
         <v>1.0</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.9358995733986685</v>
+        <v>0.9679497866993343</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.20823839484379683</v>
+        <v>0.5927555610582621</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.20823839484379683</v>
+        <v>0.5927555610582621</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.20823839484379683</v>
+        <v>0.5927555610582621</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.20823839484379683</v>
+        <v>0.5927555610582621</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -710,7 +710,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.9505494505494506</v>
+        <v>0.9752747252747254</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.9479679418074511</v>
+        <v>0.9739839709037256</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.9479679418074511</v>
+        <v>0.9739839709037256</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.8310313886613941</v>
+        <v>0.915515694330697</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.8173589500532631</v>
+        <v>0.9086794750266316</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
     </row>
     <row r="13">
@@ -809,19 +809,19 @@
         <v>1.0</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.797979797979798</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.797979797979798</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.797979797979798</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.797979797979798</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.797979797979798</v>
+        <v>0.898989898989899</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.654945054945055</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.5141414141414141</v>
+        <v>0.6638503680876562</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.34276094276094277</v>
+        <v>0.5956228956228956</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.31737373737373736</v>
+        <v>0.5460108123488405</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.45339105339105334</v>
+        <v>0.6552669552669552</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.45339105339105334</v>
+        <v>0.6334751877124758</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.5425925925925926</v>
+        <v>0.6787037037037038</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.4650793650793651</v>
+        <v>0.6737161531279179</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.1554537437870771</v>
+        <v>0.5382531876830122</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.451111111111111</v>
+        <v>0.6814379084967319</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.451111111111111</v>
+        <v>0.6814379084967319</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.451111111111111</v>
+        <v>0.6814379084967319</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.509776570048309</v>
+        <v>0.7103338295786099</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.509776570048309</v>
+        <v>0.7103338295786099</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.509776570048309</v>
+        <v>0.7103338295786099</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.509776570048309</v>
+        <v>0.7103338295786099</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.509776570048309</v>
+        <v>0.7103338295786099</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.45239130434782604</v>
+        <v>0.6820780051150894</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.5191919191919193</v>
+        <v>0.7448900772430185</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7354166666666666</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.3481481481481482</v>
+        <v>0.6248937462052216</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6464285714285715</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5020833333333334</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.3380681818181818</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.35683139534883723</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.36875</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.36875</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.08166666666666667</v>
+        <v>0.38805555555555554</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.08166666666666667</v>
+        <v>0.38805555555555554</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.08166666666666667</v>
+        <v>0.38805555555555554</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.08166666666666667</v>
+        <v>0.38805555555555554</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.736547619047619</v>
+        <v>0.8277332689832689</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.4832589285714286</v>
+        <v>0.6077008928571429</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.7365476190476191</v>
+        <v>0.7315550595238096</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.035947010383100615</v>
+        <v>0.4566238119400166</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.20566502463054187</v>
+        <v>0.4821428571428571</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.14393939393939395</v>
+        <v>0.4801329622758194</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.12962962962962962</v>
+        <v>0.469070133963751</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.1088154269972452</v>
+        <v>0.4606577134986226</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.1088154269972452</v>
+        <v>0.4606577134986226</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.0944055944055944</v>
+        <v>0.4727347120964142</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.7112103174603175</v>
+        <v>0.8556051587301587</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.38061868686868694</v>
+        <v>0.6903093434343435</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.19717261904761907</v>
+        <v>0.5985863095238095</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.19717261904761907</v>
+        <v>0.5985863095238095</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.4062074829931973</v>
+        <v>0.6640412414965986</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.036458333333333336</v>
+        <v>0.3667140151515152</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.036458333333333336</v>
+        <v>0.3667140151515152</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.036458333333333336</v>
+        <v>0.3667140151515152</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.036458333333333336</v>
+        <v>0.3667140151515152</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.036458333333333336</v>
+        <v>0.3667140151515152</v>
       </c>
     </row>
     <row r="21">
@@ -1090,34 +1090,34 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>1.0</v>
+        <v>0.95</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="22">
@@ -1132,31 +1132,31 @@
         </is>
       </c>
       <c r="C22" s="0" t="n">
-        <v>0.25783208020050125</v>
+        <v>0.5955827067669173</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.26309523809523805</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.26309523809523805</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
     </row>
     <row r="23">

--- a/all_sim/det_gemini_pet.xlsx
+++ b/all_sim/det_gemini_pet.xlsx
@@ -332,11 +332,11 @@
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.6678516313932981</v>
+        <v>0.3891920194003528</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.8042929292929293</v>
+        <v>0.6195286195286196</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.6769607843137255</v>
+        <v>0.3720588235294118</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.8231566820276497</v>
+        <v>0.6566820276497696</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -464,31 +464,31 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.8869047619047619</v>
+        <v>0.7738095238095237</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.8869047619047619</v>
+        <v>0.7738095238095237</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.8869047619047619</v>
+        <v>0.7738095238095237</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.8869047619047619</v>
+        <v>0.7738095238095237</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.861904761904762</v>
+        <v>0.7238095238095238</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.8452380952380951</v>
+        <v>0.6904761904761904</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.8452380952380951</v>
+        <v>0.6904761904761904</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.8452380952380951</v>
+        <v>0.6904761904761904</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.8452380952380951</v>
+        <v>0.6904761904761904</v>
       </c>
     </row>
     <row r="5">
@@ -510,22 +510,22 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -544,25 +544,25 @@
         <v>1.0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.9583333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.9583333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.9690970545630131</v>
+        <v>0.938676967648479</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.8779359921848454</v>
+        <v>0.7580275229357798</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.7589709027531577</v>
+        <v>0.522442132982219</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.7588066360365813</v>
+        <v>0.5221167284389056</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.7623313677867802</v>
+        <v>0.5291408305717437</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.7566148945235075</v>
+        <v>0.5178178162233381</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.7566148945235075</v>
+        <v>0.5178178162233381</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.7566148945235075</v>
+        <v>0.5178178162233381</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.7566148945235075</v>
+        <v>0.5178178162233381</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.7566148945235075</v>
+        <v>0.5178178162233381</v>
       </c>
     </row>
     <row r="8">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9872148142745253</v>
+        <v>0.9744296285490506</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.9872148142745253</v>
+        <v>0.9744296285490506</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>1.0</v>
@@ -624,19 +624,19 @@
         <v>1.0</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.9679497866993343</v>
+        <v>0.9358995733986685</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.5927555610582621</v>
+        <v>0.20350570405189236</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.5927555610582621</v>
+        <v>0.20350570405189236</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.5927555610582621</v>
+        <v>0.20350570405189236</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.5927555610582621</v>
+        <v>0.20350570405189236</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
     </row>
     <row r="10">
@@ -710,7 +710,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.9752747252747254</v>
+        <v>0.9505494505494506</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.9739839709037256</v>
+        <v>0.9479679418074511</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.9739839709037256</v>
+        <v>0.9479679418074511</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.915515694330697</v>
+        <v>0.8310313886613941</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.9086794750266316</v>
+        <v>0.8173589500532631</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
     </row>
     <row r="13">
@@ -809,19 +809,19 @@
         <v>1.0</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.898989898989899</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.898989898989899</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.898989898989899</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.898989898989899</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.898989898989899</v>
+        <v>0.797979797979798</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.654945054945055</v>
+        <v>0.421978021978022</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.6638503680876562</v>
+        <v>0.41828454031843865</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5956228956228956</v>
+        <v>0.2908274665850424</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.5460108123488405</v>
+        <v>0.2458528951486698</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.6552669552669552</v>
+        <v>0.38862090290661716</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.6334751877124758</v>
+        <v>0.36886051801306036</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.6787037037037038</v>
+        <v>0.44211248285322363</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.6737161531279179</v>
+        <v>0.4103641456582633</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.5382531876830122</v>
+        <v>0.1431810798038868</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.6814379084967319</v>
+        <v>0.4113071895424836</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.6814379084967319</v>
+        <v>0.4113071895424836</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.6814379084967319</v>
+        <v>0.4113071895424836</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.7103338295786099</v>
+        <v>0.4643509350935092</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.7103338295786099</v>
+        <v>0.4643509350935092</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.7103338295786099</v>
+        <v>0.4643509350935092</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.7103338295786099</v>
+        <v>0.4643509350935092</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.7103338295786099</v>
+        <v>0.4643509350935092</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.6820780051150894</v>
+        <v>0.4124744245524296</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.7448900772430185</v>
+        <v>0.5039215686274511</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.7354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.6248937462052216</v>
+        <v>0.3139040680024287</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.6464285714285715</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.5020833333333334</v>
+        <v>0.2416666666666667</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.3380681818181818</v>
+        <v>0.03835227272727273</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.35683139534883723</v>
+        <v>0.040697674418604654</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.36875</v>
+        <v>0.0421875</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.36875</v>
+        <v>0.0421875</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.38805555555555554</v>
+        <v>0.05671296296296296</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.38805555555555554</v>
+        <v>0.05671296296296296</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.38805555555555554</v>
+        <v>0.05671296296296296</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.38805555555555554</v>
+        <v>0.05671296296296296</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.8277332689832689</v>
+        <v>0.6768275418275418</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.6077008928571429</v>
+        <v>0.3538145727040817</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.7315550595238096</v>
+        <v>0.5351478794642858</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.4566238119400166</v>
+        <v>0.03153633426247478</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.4821428571428571</v>
+        <v>0.1560217428231697</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.4801329622758194</v>
+        <v>0.11750154607297465</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.469070133963751</v>
+        <v>0.10480693459416864</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.4606577134986226</v>
+        <v>0.08841253443526172</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.4606577134986226</v>
+        <v>0.08841253443526172</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.4727347120964142</v>
+        <v>0.08034518672816544</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.8556051587301587</v>
+        <v>0.7112103174603175</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.6903093434343435</v>
+        <v>0.38061868686868694</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.5985863095238095</v>
+        <v>0.19717261904761907</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.5985863095238095</v>
+        <v>0.19717261904761907</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.6640412414965986</v>
+        <v>0.3744725233843538</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.3667140151515152</v>
+        <v>0.02541035353535354</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.3667140151515152</v>
+        <v>0.02541035353535354</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.3667140151515152</v>
+        <v>0.02541035353535354</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.3667140151515152</v>
+        <v>0.02541035353535354</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.3667140151515152</v>
+        <v>0.02541035353535354</v>
       </c>
     </row>
     <row r="21">
@@ -1090,34 +1090,34 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
     </row>
     <row r="22">
@@ -1132,31 +1132,31 @@
         </is>
       </c>
       <c r="C22" s="0" t="n">
-        <v>0.5955827067669173</v>
+        <v>0.24064327485380116</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.5982142857142857</v>
+        <v>0.24555555555555553</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.5982142857142857</v>
+        <v>0.24555555555555553</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
     </row>
     <row r="23">
